--- a/ball_at_teammate_normalized_prototype_v1_executable.xlsx
+++ b/ball_at_teammate_normalized_prototype_v1_executable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="normalized_teammate_scenes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="verification" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="semantic_rules" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="normalized_teammate_scenes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="verification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="semantic_rules" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>отдать пас назад || продвигаться вперед</t>
+          <t>Осматривается в поиске партнеров</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
